--- a/templates/zayavka_perevezennia_template.xlsx
+++ b/templates/zayavka_perevezennia_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Ovoprime\AI\Заявка на перевезення\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A39ABAD-758A-4E72-9563-E101B18F3FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286CC0CE-A9DF-4211-AF97-B9AFBB283EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -327,7 +327,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -350,6 +350,11 @@
     <font>
       <sz val="10"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Carlito"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -378,7 +383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -395,41 +400,40 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,93 +606,93 @@
   <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="6" style="9" customWidth="1"/>
-    <col min="2" max="2" width="25" style="9" customWidth="1"/>
-    <col min="3" max="3" width="11" style="9" customWidth="1"/>
-    <col min="4" max="4" width="8.75" style="9" customWidth="1"/>
-    <col min="5" max="5" width="27.625" style="9" customWidth="1"/>
-    <col min="6" max="7" width="12" style="9" customWidth="1"/>
-    <col min="8" max="8" width="18" style="9" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="6" style="6" customWidth="1"/>
+    <col min="2" max="2" width="19.125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="11" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="6" customWidth="1"/>
+    <col min="5" max="5" width="27.375" style="6" customWidth="1"/>
+    <col min="6" max="7" width="12" style="6" customWidth="1"/>
+    <col min="8" max="8" width="18" style="6" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1">
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="9" t="s">
+      <c r="D1" s="17"/>
+      <c r="E1" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="21.95" customHeight="1">
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" spans="1:19" ht="21.95" customHeight="1">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+    </row>
+    <row r="3" spans="1:19" ht="22.5" customHeight="1">
       <c r="B3" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="30">
+    <row r="5" spans="1:19" ht="44.25" customHeight="1">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="20"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="19"/>
       <c r="H5" s="2"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="3">
         <v>1</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="10" t="s">
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="3">
         <v>2</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="10" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -697,498 +701,526 @@
       <c r="A9" s="3">
         <v>3</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="10" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="3">
         <v>4</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="10" t="s">
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
     </row>
     <row r="11" spans="1:19" ht="42" customHeight="1">
       <c r="A11" s="3">
         <v>5</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="10" t="s">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="3">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="10" t="s">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="3">
         <v>7</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="10" t="s">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="3">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="10" t="s">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="3">
         <v>9</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="10" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="3">
         <v>10</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="10" t="s">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="30" customHeight="1">
       <c r="A17" s="3">
         <v>11</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="10" t="s">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1">
       <c r="A18" s="3">
         <v>12</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="10" t="s">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="58.5" customHeight="1">
       <c r="A19" s="3">
         <v>13</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="10" t="s">
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="42" customHeight="1">
       <c r="A20" s="3">
         <v>14</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="10" t="s">
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" ht="42" customHeight="1">
       <c r="A21" s="3">
         <v>15</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="10" t="s">
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1">
       <c r="A22" s="3">
         <v>16</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="10" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1">
       <c r="A23" s="3">
         <v>17</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="10" t="s">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="42" customHeight="1">
       <c r="A24" s="3">
         <v>18</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="10" t="s">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="27" spans="1:8" ht="36" customHeight="1">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" ht="36" customHeight="1">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:8" ht="36" customHeight="1">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" ht="36" customHeight="1">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:8" ht="36" customHeight="1">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
     </row>
     <row r="33" spans="1:8" ht="36" customHeight="1">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" ht="36" customHeight="1">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
     </row>
     <row r="37" spans="1:8" ht="15">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
     </row>
     <row r="38" spans="1:8" ht="15">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="16"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="11"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11" t="s">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="16"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="11"/>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11" t="s">
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="16"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="11"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11" t="s">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11" t="s">
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11" t="s">
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11" t="s">
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A38:D38"/>
+  <mergeCells count="69">
+    <mergeCell ref="L9:S9"/>
+    <mergeCell ref="L10:S10"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="M8:P8"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E23:F23"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="E38:F38"/>
@@ -1198,49 +1230,22 @@
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="L9:S9"/>
-    <mergeCell ref="L10:S10"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="M8:P8"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E42:F42"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
